--- a/results/20250624/evaluation_CHD_49_noisy_0.3_bopos.xlsx
+++ b/results/20250624/evaluation_CHD_49_noisy_0.3_bopos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I113"/>
+  <dimension ref="A1:I185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -621,14 +621,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>mfrd</t>
+          <t>jaccard</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.88308</v>
+        <v>0.47866</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05103</v>
+        <v>0.03159</v>
       </c>
     </row>
     <row r="6">
@@ -660,14 +660,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>afrd</t>
+          <t>macro_f1</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.46102</v>
+        <v>0.51588</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.03447</v>
       </c>
     </row>
     <row r="7">
@@ -694,19 +694,19 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>hamming_accuracy_pa</t>
+          <t>micro_f1</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.63396</v>
+        <v>0.63364</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02693</v>
+        <v>0.02717</v>
       </c>
     </row>
     <row r="8">
@@ -733,19 +733,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>subset0_1_pa</t>
+          <t>macro_precision</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.0723</v>
+        <v>0.45301</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0256</v>
+        <v>0.03259</v>
       </c>
     </row>
     <row r="9">
@@ -772,19 +772,19 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>f1_pa</t>
+          <t>micro_precision</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.6069600000000001</v>
+        <v>0.54928</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0353</v>
+        <v>0.03339</v>
       </c>
     </row>
     <row r="10">
@@ -811,19 +811,19 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>arec</t>
+          <t>macro_recall</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.64264</v>
+        <v>0.62554</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02671</v>
+        <v>0.06904</v>
       </c>
     </row>
     <row r="11">
@@ -850,19 +850,19 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>aabs</t>
+          <t>micro_recall</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.02372</v>
+        <v>0.75036</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01477</v>
+        <v>0.02946</v>
       </c>
     </row>
     <row r="12">
@@ -889,19 +889,19 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>example_precision</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.07477</v>
+        <v>0.55722</v>
       </c>
       <c r="I12" t="n">
-        <v>0.02734</v>
+        <v>0.04036</v>
       </c>
     </row>
     <row r="13">
@@ -928,19 +928,19 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>abs</t>
+          <t>example_recall</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.1027</v>
+        <v>0.74203</v>
       </c>
       <c r="I13" t="n">
-        <v>0.05084</v>
+        <v>0.0405</v>
       </c>
     </row>
     <row r="14">
@@ -967,19 +967,19 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PreferenceOrder</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>hamming_accuracy_PRE_ORDER</t>
+          <t>mfrd</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.41808</v>
+        <v>0.88308</v>
       </c>
       <c r="I14" t="n">
-        <v>0.02091</v>
+        <v>0.05103</v>
       </c>
     </row>
     <row r="15">
@@ -1006,19 +1006,19 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PreferenceOrder</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>subset0_1_PRE_ORDER</t>
+          <t>afrd</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.01081</v>
+        <v>0.46102</v>
       </c>
       <c r="I15" t="n">
-        <v>0.007849999999999999</v>
+        <v>0.07240000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PreOrder__Hamming__2</t>
+          <t>PreOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1037,9 +1037,7 @@
           <t>Hamming</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>2</v>
-      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -1047,19 +1045,19 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>BinaryVector</t>
+          <t>PartialAbstention</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>hamming_accuracy</t>
+          <t>hamming_accuracy_pa</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.63874</v>
+        <v>0.63396</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01917</v>
+        <v>0.02693</v>
       </c>
     </row>
     <row r="17">
@@ -1070,7 +1068,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PreOrder__Hamming__2</t>
+          <t>PreOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1078,9 +1076,7 @@
           <t>Hamming</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>2</v>
-      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -1088,19 +1084,19 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>BinaryVector</t>
+          <t>PartialAbstention</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>subset0_1</t>
+          <t>subset0_1_pa</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.07658</v>
+        <v>0.0723</v>
       </c>
       <c r="I17" t="n">
-        <v>0.02103</v>
+        <v>0.0256</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1107,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PreOrder__Hamming__2</t>
+          <t>PreOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1119,9 +1115,7 @@
           <t>Hamming</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>2</v>
-      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -1129,19 +1123,19 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>BinaryVector</t>
+          <t>PartialAbstention</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>f1</t>
+          <t>f1_pa</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.54595</v>
+        <v>0.6069600000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>0.02877</v>
+        <v>0.0353</v>
       </c>
     </row>
     <row r="19">
@@ -1152,7 +1146,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PreOrder__Hamming__2</t>
+          <t>PreOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1160,9 +1154,7 @@
           <t>Hamming</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>2</v>
-      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -1170,19 +1162,19 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BinaryVector</t>
+          <t>PartialAbstention</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>mfrd</t>
+          <t>arec</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.90226</v>
+        <v>0.64264</v>
       </c>
       <c r="I19" t="n">
-        <v>0.09540999999999999</v>
+        <v>0.02671</v>
       </c>
     </row>
     <row r="20">
@@ -1193,7 +1185,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PreOrder__Hamming__2</t>
+          <t>PreOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1201,9 +1193,7 @@
           <t>Hamming</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>2</v>
-      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -1211,19 +1201,19 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BinaryVector</t>
+          <t>PartialAbstention</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>afrd</t>
+          <t>aabs</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.44693</v>
+        <v>0.02372</v>
       </c>
       <c r="I20" t="n">
-        <v>0.06666999999999999</v>
+        <v>0.01477</v>
       </c>
     </row>
     <row r="21">
@@ -1234,7 +1224,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PreOrder__Hamming__2</t>
+          <t>PreOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1242,9 +1232,7 @@
           <t>Hamming</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>2</v>
-      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -1257,14 +1245,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>hamming_accuracy_pa</t>
+          <t>rec</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.64446</v>
+        <v>0.07477</v>
       </c>
       <c r="I21" t="n">
-        <v>0.01954</v>
+        <v>0.02734</v>
       </c>
     </row>
     <row r="22">
@@ -1275,7 +1263,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PreOrder__Hamming__2</t>
+          <t>PreOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1283,9 +1271,7 @@
           <t>Hamming</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>2</v>
-      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -1298,14 +1284,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>subset0_1_pa</t>
+          <t>abs</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.0839</v>
+        <v>0.1027</v>
       </c>
       <c r="I22" t="n">
-        <v>0.01794</v>
+        <v>0.05084</v>
       </c>
     </row>
     <row r="23">
@@ -1316,7 +1302,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PreOrder__Hamming__2</t>
+          <t>PreOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1324,9 +1310,7 @@
           <t>Hamming</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>2</v>
-      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -1334,19 +1318,19 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>PreferenceOrder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>f1_pa</t>
+          <t>hamming_accuracy_PRE_ORDER</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.54581</v>
+        <v>0.41808</v>
       </c>
       <c r="I23" t="n">
-        <v>0.03068</v>
+        <v>0.02091</v>
       </c>
     </row>
     <row r="24">
@@ -1357,7 +1341,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PreOrder__Hamming__2</t>
+          <t>PreOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1365,9 +1349,7 @@
           <t>Hamming</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>2</v>
-      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -1375,19 +1357,19 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>PreferenceOrder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>arec</t>
+          <t>subset0_1_PRE_ORDER</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.6518</v>
+        <v>0.01081</v>
       </c>
       <c r="I24" t="n">
-        <v>0.02027</v>
+        <v>0.007849999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1416,19 +1398,19 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>aabs</t>
+          <t>hamming_accuracy</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.02072</v>
+        <v>0.63874</v>
       </c>
       <c r="I25" t="n">
-        <v>0.01402</v>
+        <v>0.01917</v>
       </c>
     </row>
     <row r="26">
@@ -1457,19 +1439,19 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>subset0_1</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.08559</v>
+        <v>0.07658</v>
       </c>
       <c r="I26" t="n">
-        <v>0.01624</v>
+        <v>0.02103</v>
       </c>
     </row>
     <row r="27">
@@ -1498,19 +1480,19 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>abs</t>
+          <t>f1</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.08018</v>
+        <v>0.54595</v>
       </c>
       <c r="I27" t="n">
-        <v>0.04842</v>
+        <v>0.02877</v>
       </c>
     </row>
     <row r="28">
@@ -1539,19 +1521,19 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PreferenceOrder</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>hamming_accuracy_PRE_ORDER</t>
+          <t>jaccard</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.39261</v>
+        <v>0.42626</v>
       </c>
       <c r="I28" t="n">
-        <v>0.01492</v>
+        <v>0.02552</v>
       </c>
     </row>
     <row r="29">
@@ -1580,19 +1562,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PreferenceOrder</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>subset0_1_PRE_ORDER</t>
+          <t>macro_f1</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.0027</v>
+        <v>0.43767</v>
       </c>
       <c r="I29" t="n">
-        <v>0.00413</v>
+        <v>0.02936</v>
       </c>
     </row>
     <row r="30">
@@ -1603,15 +1585,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__None</t>
+          <t>PreOrder__Hamming__2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -1624,14 +1608,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>hamming_accuracy</t>
+          <t>micro_f1</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.62508</v>
+        <v>0.57039</v>
       </c>
       <c r="I30" t="n">
-        <v>0.02747</v>
+        <v>0.0257</v>
       </c>
     </row>
     <row r="31">
@@ -1642,15 +1626,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__None</t>
+          <t>PreOrder__Hamming__2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -1663,14 +1649,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>subset0_1</t>
+          <t>macro_precision</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.06486</v>
+        <v>0.45873</v>
       </c>
       <c r="I31" t="n">
-        <v>0.02342</v>
+        <v>0.03518</v>
       </c>
     </row>
     <row r="32">
@@ -1681,15 +1667,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__None</t>
+          <t>PreOrder__Hamming__2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -1702,14 +1690,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>f1</t>
+          <t>micro_precision</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.60553</v>
+        <v>0.58405</v>
       </c>
       <c r="I32" t="n">
-        <v>0.03441</v>
+        <v>0.03752</v>
       </c>
     </row>
     <row r="33">
@@ -1720,15 +1708,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__None</t>
+          <t>PreOrder__Hamming__2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -1741,14 +1731,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>mfrd</t>
+          <t>macro_recall</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.88309</v>
+        <v>0.43071</v>
       </c>
       <c r="I33" t="n">
-        <v>0.05115</v>
+        <v>0.02735</v>
       </c>
     </row>
     <row r="34">
@@ -1759,15 +1749,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__None</t>
+          <t>PreOrder__Hamming__2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -1780,14 +1772,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>afrd</t>
+          <t>micro_recall</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.46507</v>
+        <v>0.5581700000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>0.07298</v>
+        <v>0.02066</v>
       </c>
     </row>
     <row r="35">
@@ -1798,15 +1790,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__None</t>
+          <t>PreOrder__Hamming__2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -1814,19 +1808,19 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>hamming_accuracy_pa</t>
+          <t>example_precision</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.63217</v>
+        <v>0.5948</v>
       </c>
       <c r="I35" t="n">
-        <v>0.02747</v>
+        <v>0.04014</v>
       </c>
     </row>
     <row r="36">
@@ -1837,15 +1831,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__None</t>
+          <t>PreOrder__Hamming__2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -1853,19 +1849,19 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>subset0_1_pa</t>
+          <t>example_recall</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.07413</v>
+        <v>0.55566</v>
       </c>
       <c r="I36" t="n">
-        <v>0.02746</v>
+        <v>0.02317</v>
       </c>
     </row>
     <row r="37">
@@ -1876,15 +1872,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__None</t>
+          <t>PreOrder__Hamming__2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -1892,19 +1890,19 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>f1_pa</t>
+          <t>mfrd</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.60599</v>
+        <v>0.90226</v>
       </c>
       <c r="I37" t="n">
-        <v>0.03539</v>
+        <v>0.09540999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1915,15 +1913,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__None</t>
+          <t>PreOrder__Hamming__2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -1931,19 +1931,19 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>arec</t>
+          <t>afrd</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.64129</v>
+        <v>0.44693</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0271</v>
+        <v>0.06666999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -1954,15 +1954,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__None</t>
+          <t>PreOrder__Hamming__2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -1975,14 +1977,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>aabs</t>
+          <t>hamming_accuracy_pa</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.02477</v>
+        <v>0.64446</v>
       </c>
       <c r="I39" t="n">
-        <v>0.01436</v>
+        <v>0.01954</v>
       </c>
     </row>
     <row r="40">
@@ -1993,15 +1995,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__None</t>
+          <t>PreOrder__Hamming__2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -2014,14 +2018,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>subset0_1_pa</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.07658</v>
+        <v>0.0839</v>
       </c>
       <c r="I40" t="n">
-        <v>0.02968</v>
+        <v>0.01794</v>
       </c>
     </row>
     <row r="41">
@@ -2032,15 +2036,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__None</t>
+          <t>PreOrder__Hamming__2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -2053,14 +2059,14 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>abs</t>
+          <t>f1_pa</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.10901</v>
+        <v>0.54581</v>
       </c>
       <c r="I41" t="n">
-        <v>0.04909</v>
+        <v>0.03068</v>
       </c>
     </row>
     <row r="42">
@@ -2071,15 +2077,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__None</t>
+          <t>PreOrder__Hamming__2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -2087,19 +2095,19 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PreferenceOrder</t>
+          <t>PartialAbstention</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>hamming_accuracy_PRE_ORDER</t>
+          <t>arec</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.41508</v>
+        <v>0.6518</v>
       </c>
       <c r="I42" t="n">
-        <v>0.02088</v>
+        <v>0.02027</v>
       </c>
     </row>
     <row r="43">
@@ -2110,15 +2118,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__None</t>
+          <t>PreOrder__Hamming__2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -2126,19 +2136,19 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PreferenceOrder</t>
+          <t>PartialAbstention</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>subset0_1_PRE_ORDER</t>
+          <t>aabs</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.01081</v>
+        <v>0.02072</v>
       </c>
       <c r="I43" t="n">
-        <v>0.007849999999999999</v>
+        <v>0.01402</v>
       </c>
     </row>
     <row r="44">
@@ -2149,12 +2159,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__2</t>
+          <t>PreOrder__Hamming__2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Subset</t>
+          <t>Hamming</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -2167,19 +2177,19 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>BinaryVector</t>
+          <t>PartialAbstention</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>hamming_accuracy</t>
+          <t>rec</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.63664</v>
+        <v>0.08559</v>
       </c>
       <c r="I44" t="n">
-        <v>0.01817</v>
+        <v>0.01624</v>
       </c>
     </row>
     <row r="45">
@@ -2190,12 +2200,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__2</t>
+          <t>PreOrder__Hamming__2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Subset</t>
+          <t>Hamming</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2208,19 +2218,19 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>BinaryVector</t>
+          <t>PartialAbstention</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>subset0_1</t>
+          <t>abs</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.07387000000000001</v>
+        <v>0.08018</v>
       </c>
       <c r="I45" t="n">
-        <v>0.01924</v>
+        <v>0.04842</v>
       </c>
     </row>
     <row r="46">
@@ -2231,12 +2241,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__2</t>
+          <t>PreOrder__Hamming__2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Subset</t>
+          <t>Hamming</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2249,19 +2259,19 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>BinaryVector</t>
+          <t>PreferenceOrder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>f1</t>
+          <t>hamming_accuracy_PRE_ORDER</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.53205</v>
+        <v>0.39261</v>
       </c>
       <c r="I46" t="n">
-        <v>0.02842</v>
+        <v>0.01492</v>
       </c>
     </row>
     <row r="47">
@@ -2272,12 +2282,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__2</t>
+          <t>PreOrder__Hamming__2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Subset</t>
+          <t>Hamming</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2290,19 +2300,19 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>BinaryVector</t>
+          <t>PreferenceOrder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>mfrd</t>
+          <t>subset0_1_PRE_ORDER</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.87596</v>
+        <v>0.0027</v>
       </c>
       <c r="I47" t="n">
-        <v>0.12507</v>
+        <v>0.00413</v>
       </c>
     </row>
     <row r="48">
@@ -2313,7 +2323,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__2</t>
+          <t>PreOrder__Subset__None</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2321,9 +2331,7 @@
           <t>Subset</t>
         </is>
       </c>
-      <c r="D48" t="n">
-        <v>2</v>
-      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -2336,14 +2344,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>afrd</t>
+          <t>hamming_accuracy</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.44156</v>
+        <v>0.62508</v>
       </c>
       <c r="I48" t="n">
-        <v>0.06537999999999999</v>
+        <v>0.02747</v>
       </c>
     </row>
     <row r="49">
@@ -2354,7 +2362,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__2</t>
+          <t>PreOrder__Subset__None</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2362,9 +2370,7 @@
           <t>Subset</t>
         </is>
       </c>
-      <c r="D49" t="n">
-        <v>2</v>
-      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -2372,19 +2378,19 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>hamming_accuracy_pa</t>
+          <t>subset0_1</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.64205</v>
+        <v>0.06486</v>
       </c>
       <c r="I49" t="n">
-        <v>0.01861</v>
+        <v>0.02342</v>
       </c>
     </row>
     <row r="50">
@@ -2395,7 +2401,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__2</t>
+          <t>PreOrder__Subset__None</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2403,9 +2409,7 @@
           <t>Subset</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>2</v>
-      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -2413,19 +2417,19 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>subset0_1_pa</t>
+          <t>f1</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.08029</v>
+        <v>0.60553</v>
       </c>
       <c r="I50" t="n">
-        <v>0.01571</v>
+        <v>0.03441</v>
       </c>
     </row>
     <row r="51">
@@ -2436,7 +2440,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__2</t>
+          <t>PreOrder__Subset__None</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2444,9 +2448,7 @@
           <t>Subset</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v>2</v>
-      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -2454,19 +2456,19 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>f1_pa</t>
+          <t>jaccard</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.53181</v>
+        <v>0.47686</v>
       </c>
       <c r="I51" t="n">
-        <v>0.03031</v>
+        <v>0.03225</v>
       </c>
     </row>
     <row r="52">
@@ -2477,7 +2479,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__2</t>
+          <t>PreOrder__Subset__None</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2485,9 +2487,7 @@
           <t>Subset</t>
         </is>
       </c>
-      <c r="D52" t="n">
-        <v>2</v>
-      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -2495,19 +2495,19 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>arec</t>
+          <t>macro_f1</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.64925</v>
+        <v>0.5139</v>
       </c>
       <c r="I52" t="n">
-        <v>0.01891</v>
+        <v>0.03637</v>
       </c>
     </row>
     <row r="53">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__2</t>
+          <t>PreOrder__Subset__None</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2526,9 +2526,7 @@
           <t>Subset</t>
         </is>
       </c>
-      <c r="D53" t="n">
-        <v>2</v>
-      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -2536,19 +2534,19 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>aabs</t>
+          <t>micro_f1</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.02012</v>
+        <v>0.63206</v>
       </c>
       <c r="I53" t="n">
-        <v>0.01433</v>
+        <v>0.02833</v>
       </c>
     </row>
     <row r="54">
@@ -2559,7 +2557,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__2</t>
+          <t>PreOrder__Subset__None</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2567,9 +2565,7 @@
           <t>Subset</t>
         </is>
       </c>
-      <c r="D54" t="n">
-        <v>2</v>
-      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -2577,19 +2573,19 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>macro_precision</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.08198</v>
+        <v>0.45074</v>
       </c>
       <c r="I54" t="n">
-        <v>0.01363</v>
+        <v>0.03378</v>
       </c>
     </row>
     <row r="55">
@@ -2600,7 +2596,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__2</t>
+          <t>PreOrder__Subset__None</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2608,9 +2604,7 @@
           <t>Subset</t>
         </is>
       </c>
-      <c r="D55" t="n">
-        <v>2</v>
-      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -2618,19 +2612,19 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>abs</t>
+          <t>micro_precision</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.07838000000000001</v>
+        <v>0.54732</v>
       </c>
       <c r="I55" t="n">
-        <v>0.04886</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="56">
@@ -2641,7 +2635,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__2</t>
+          <t>PreOrder__Subset__None</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2649,9 +2643,7 @@
           <t>Subset</t>
         </is>
       </c>
-      <c r="D56" t="n">
-        <v>2</v>
-      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -2659,19 +2651,19 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>PreferenceOrder</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>hamming_accuracy_PRE_ORDER</t>
+          <t>macro_recall</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.39261</v>
+        <v>0.62416</v>
       </c>
       <c r="I56" t="n">
-        <v>0.01544</v>
+        <v>0.06988999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -2682,7 +2674,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PreOrder__Subset__2</t>
+          <t>PreOrder__Subset__None</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2690,9 +2682,7 @@
           <t>Subset</t>
         </is>
       </c>
-      <c r="D57" t="n">
-        <v>2</v>
-      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>PreOrder</t>
@@ -2700,19 +2690,19 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PreferenceOrder</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>subset0_1_PRE_ORDER</t>
+          <t>micro_recall</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0.0027</v>
+        <v>0.74957</v>
       </c>
       <c r="I57" t="n">
-        <v>0.00413</v>
+        <v>0.03098</v>
       </c>
     </row>
     <row r="58">
@@ -2723,18 +2713,18 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__None</t>
+          <t>PreOrder__Subset__None</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2744,14 +2734,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>hamming_accuracy</t>
+          <t>example_precision</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0.58378</v>
+        <v>0.55485</v>
       </c>
       <c r="I58" t="n">
-        <v>0.02165</v>
+        <v>0.04053</v>
       </c>
     </row>
     <row r="59">
@@ -2762,18 +2752,18 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__None</t>
+          <t>PreOrder__Subset__None</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2783,14 +2773,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>subset0_1</t>
+          <t>example_recall</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0.04955</v>
+        <v>0.74128</v>
       </c>
       <c r="I59" t="n">
-        <v>0.01943</v>
+        <v>0.04129</v>
       </c>
     </row>
     <row r="60">
@@ -2801,18 +2791,18 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__None</t>
+          <t>PreOrder__Subset__None</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2822,14 +2812,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>f1</t>
+          <t>mfrd</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0.59832</v>
+        <v>0.88309</v>
       </c>
       <c r="I60" t="n">
-        <v>0.02656</v>
+        <v>0.05115</v>
       </c>
     </row>
     <row r="61">
@@ -2840,18 +2830,18 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__None</t>
+          <t>PreOrder__Subset__None</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2861,14 +2851,14 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>mfrd</t>
+          <t>afrd</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.85219</v>
+        <v>0.46507</v>
       </c>
       <c r="I61" t="n">
-        <v>0.05026</v>
+        <v>0.07298</v>
       </c>
     </row>
     <row r="62">
@@ -2879,35 +2869,35 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__None</t>
+          <t>PreOrder__Subset__None</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>BinaryVector</t>
+          <t>PartialAbstention</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>afrd</t>
+          <t>hamming_accuracy_pa</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0.49316</v>
+        <v>0.63217</v>
       </c>
       <c r="I62" t="n">
-        <v>0.06327000000000001</v>
+        <v>0.02747</v>
       </c>
     </row>
     <row r="63">
@@ -2918,18 +2908,18 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__None</t>
+          <t>PreOrder__Subset__None</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2939,14 +2929,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>hamming_accuracy_pa</t>
+          <t>subset0_1_pa</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0.65752</v>
+        <v>0.07413</v>
       </c>
       <c r="I63" t="n">
-        <v>0.02966</v>
+        <v>0.02746</v>
       </c>
     </row>
     <row r="64">
@@ -2957,18 +2947,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__None</t>
+          <t>PreOrder__Subset__None</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2978,14 +2968,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>subset0_1_pa</t>
+          <t>f1_pa</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0.23186</v>
+        <v>0.60599</v>
       </c>
       <c r="I64" t="n">
-        <v>0.05621</v>
+        <v>0.03539</v>
       </c>
     </row>
     <row r="65">
@@ -2996,18 +2986,18 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__None</t>
+          <t>PreOrder__Subset__None</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3017,14 +3007,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>f1_pa</t>
+          <t>arec</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0.5889799999999999</v>
+        <v>0.64129</v>
       </c>
       <c r="I65" t="n">
-        <v>0.04674</v>
+        <v>0.0271</v>
       </c>
     </row>
     <row r="66">
@@ -3035,18 +3025,18 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__None</t>
+          <t>PreOrder__Subset__None</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3056,14 +3046,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>arec</t>
+          <t>aabs</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0.77222</v>
+        <v>0.02477</v>
       </c>
       <c r="I66" t="n">
-        <v>0.03242</v>
+        <v>0.01436</v>
       </c>
     </row>
     <row r="67">
@@ -3074,18 +3064,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__None</t>
+          <t>PreOrder__Subset__None</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3095,14 +3085,14 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>aabs</t>
+          <t>rec</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0.33634</v>
+        <v>0.07658</v>
       </c>
       <c r="I67" t="n">
-        <v>0.06214</v>
+        <v>0.02968</v>
       </c>
     </row>
     <row r="68">
@@ -3113,18 +3103,18 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__None</t>
+          <t>PreOrder__Subset__None</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3134,14 +3124,14 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>abs</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0.27027</v>
+        <v>0.10901</v>
       </c>
       <c r="I68" t="n">
-        <v>0.07285999999999999</v>
+        <v>0.04909</v>
       </c>
     </row>
     <row r="69">
@@ -3152,35 +3142,35 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__None</t>
+          <t>PreOrder__Subset__None</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>PreferenceOrder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>abs</t>
+          <t>hamming_accuracy_PRE_ORDER</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0.81351</v>
+        <v>0.41508</v>
       </c>
       <c r="I69" t="n">
-        <v>0.03372</v>
+        <v>0.02088</v>
       </c>
     </row>
     <row r="70">
@@ -3191,18 +3181,18 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__None</t>
+          <t>PreOrder__Subset__None</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3212,14 +3202,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>hamming_accuracy_PARTIAL_ORDER</t>
+          <t>subset0_1_PRE_ORDER</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0.48865</v>
+        <v>0.01081</v>
       </c>
       <c r="I70" t="n">
-        <v>0.01236</v>
+        <v>0.007849999999999999</v>
       </c>
     </row>
     <row r="71">
@@ -3230,35 +3220,37 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__None</t>
+          <t>PreOrder__Subset__2</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hamming</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2</v>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>PreferenceOrder</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>subset0_1_PARTIAL_ORDER</t>
+          <t>hamming_accuracy</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0.0018</v>
+        <v>0.63664</v>
       </c>
       <c r="I71" t="n">
-        <v>0.0036</v>
+        <v>0.01817</v>
       </c>
     </row>
     <row r="72">
@@ -3269,12 +3261,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__2</t>
+          <t>PreOrder__Subset__2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -3282,7 +3274,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3292,14 +3284,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>hamming_accuracy</t>
+          <t>subset0_1</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0.58318</v>
+        <v>0.07387000000000001</v>
       </c>
       <c r="I72" t="n">
-        <v>0.02324</v>
+        <v>0.01924</v>
       </c>
     </row>
     <row r="73">
@@ -3310,12 +3302,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__2</t>
+          <t>PreOrder__Subset__2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -3323,7 +3315,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3333,14 +3325,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>subset0_1</t>
+          <t>f1</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0.05045</v>
+        <v>0.53205</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0214</v>
+        <v>0.02842</v>
       </c>
     </row>
     <row r="74">
@@ -3351,12 +3343,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__2</t>
+          <t>PreOrder__Subset__2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3364,7 +3356,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3374,14 +3366,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>f1</t>
+          <t>jaccard</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>0.59492</v>
+        <v>0.41417</v>
       </c>
       <c r="I74" t="n">
-        <v>0.02851</v>
+        <v>0.02444</v>
       </c>
     </row>
     <row r="75">
@@ -3392,12 +3384,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__2</t>
+          <t>PreOrder__Subset__2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3405,7 +3397,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3415,14 +3407,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>mfrd</t>
+          <t>macro_f1</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0.84227</v>
+        <v>0.43071</v>
       </c>
       <c r="I75" t="n">
-        <v>0.04654</v>
+        <v>0.03095</v>
       </c>
     </row>
     <row r="76">
@@ -3433,12 +3425,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__2</t>
+          <t>PreOrder__Subset__2</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3446,7 +3438,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3456,14 +3448,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>afrd</t>
+          <t>micro_f1</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0.4822</v>
+        <v>0.55808</v>
       </c>
       <c r="I76" t="n">
-        <v>0.06396</v>
+        <v>0.02548</v>
       </c>
     </row>
     <row r="77">
@@ -3474,12 +3466,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__2</t>
+          <t>PreOrder__Subset__2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3487,24 +3479,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>hamming_accuracy_pa</t>
+          <t>macro_precision</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0.65642</v>
+        <v>0.46118</v>
       </c>
       <c r="I77" t="n">
-        <v>0.03232</v>
+        <v>0.03681</v>
       </c>
     </row>
     <row r="78">
@@ -3515,12 +3507,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__2</t>
+          <t>PreOrder__Subset__2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3528,24 +3520,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>subset0_1_pa</t>
+          <t>micro_precision</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>0.22635</v>
+        <v>0.58524</v>
       </c>
       <c r="I78" t="n">
-        <v>0.06183</v>
+        <v>0.0376</v>
       </c>
     </row>
     <row r="79">
@@ -3556,12 +3548,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__2</t>
+          <t>PreOrder__Subset__2</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3569,24 +3561,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>f1_pa</t>
+          <t>macro_recall</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0.58301</v>
+        <v>0.41577</v>
       </c>
       <c r="I79" t="n">
-        <v>0.04886</v>
+        <v>0.03061</v>
       </c>
     </row>
     <row r="80">
@@ -3597,12 +3589,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__2</t>
+          <t>PreOrder__Subset__2</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3610,24 +3602,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>arec</t>
+          <t>micro_recall</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>0.77177</v>
+        <v>0.53403</v>
       </c>
       <c r="I80" t="n">
-        <v>0.03368</v>
+        <v>0.02043</v>
       </c>
     </row>
     <row r="81">
@@ -3638,12 +3630,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__2</t>
+          <t>PreOrder__Subset__2</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3651,24 +3643,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>aabs</t>
+          <t>example_precision</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>0.33724</v>
+        <v>0.59676</v>
       </c>
       <c r="I81" t="n">
-        <v>0.06216</v>
+        <v>0.04001</v>
       </c>
     </row>
     <row r="82">
@@ -3679,12 +3671,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__2</t>
+          <t>PreOrder__Subset__2</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3692,24 +3684,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>example_recall</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>0.26486</v>
+        <v>0.52905</v>
       </c>
       <c r="I82" t="n">
-        <v>0.07846</v>
+        <v>0.02486</v>
       </c>
     </row>
     <row r="83">
@@ -3720,12 +3712,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__2</t>
+          <t>PreOrder__Subset__2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3733,24 +3725,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>abs</t>
+          <t>mfrd</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>0.81351</v>
+        <v>0.87596</v>
       </c>
       <c r="I83" t="n">
-        <v>0.03324</v>
+        <v>0.12507</v>
       </c>
     </row>
     <row r="84">
@@ -3761,12 +3753,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__2</t>
+          <t>PreOrder__Subset__2</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3774,24 +3766,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>PreferenceOrder</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>hamming_accuracy_PARTIAL_ORDER</t>
+          <t>afrd</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>0.48799</v>
+        <v>0.44156</v>
       </c>
       <c r="I84" t="n">
-        <v>0.01275</v>
+        <v>0.06537999999999999</v>
       </c>
     </row>
     <row r="85">
@@ -3802,12 +3794,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PartialOrder__Hamming__2</t>
+          <t>PreOrder__Subset__2</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hamming</t>
+          <t>Subset</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3815,24 +3807,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>PreferenceOrder</t>
+          <t>PartialAbstention</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>subset0_1_PARTIAL_ORDER</t>
+          <t>hamming_accuracy_pa</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>0.0018</v>
+        <v>0.64205</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0036</v>
+        <v>0.01861</v>
       </c>
     </row>
     <row r="86">
@@ -3843,7 +3835,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__None</t>
+          <t>PreOrder__Subset__2</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3851,27 +3843,29 @@
           <t>Subset</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="n">
+        <v>2</v>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>BinaryVector</t>
+          <t>PartialAbstention</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>hamming_accuracy</t>
+          <t>subset0_1_pa</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>0.58333</v>
+        <v>0.08029</v>
       </c>
       <c r="I86" t="n">
-        <v>0.02135</v>
+        <v>0.01571</v>
       </c>
     </row>
     <row r="87">
@@ -3882,7 +3876,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__None</t>
+          <t>PreOrder__Subset__2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3890,27 +3884,29 @@
           <t>Subset</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="n">
+        <v>2</v>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>BinaryVector</t>
+          <t>PartialAbstention</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>subset0_1</t>
+          <t>f1_pa</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>0.04955</v>
+        <v>0.53181</v>
       </c>
       <c r="I87" t="n">
-        <v>0.01943</v>
+        <v>0.03031</v>
       </c>
     </row>
     <row r="88">
@@ -3921,7 +3917,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__None</t>
+          <t>PreOrder__Subset__2</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3929,27 +3925,29 @@
           <t>Subset</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="n">
+        <v>2</v>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>BinaryVector</t>
+          <t>PartialAbstention</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>f1</t>
+          <t>arec</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>0.59798</v>
+        <v>0.64925</v>
       </c>
       <c r="I88" t="n">
-        <v>0.02595</v>
+        <v>0.01891</v>
       </c>
     </row>
     <row r="89">
@@ -3960,7 +3958,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__None</t>
+          <t>PreOrder__Subset__2</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3968,27 +3966,29 @@
           <t>Subset</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="n">
+        <v>2</v>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>BinaryVector</t>
+          <t>PartialAbstention</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>mfrd</t>
+          <t>aabs</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>0.85336</v>
+        <v>0.02012</v>
       </c>
       <c r="I89" t="n">
-        <v>0.04952</v>
+        <v>0.01433</v>
       </c>
     </row>
     <row r="90">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__None</t>
+          <t>PreOrder__Subset__2</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4007,27 +4007,29 @@
           <t>Subset</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="n">
+        <v>2</v>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>BinaryVector</t>
+          <t>PartialAbstention</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>afrd</t>
+          <t>rec</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>0.49298</v>
+        <v>0.08198</v>
       </c>
       <c r="I90" t="n">
-        <v>0.06448</v>
+        <v>0.01363</v>
       </c>
     </row>
     <row r="91">
@@ -4038,7 +4040,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__None</t>
+          <t>PreOrder__Subset__2</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4046,10 +4048,12 @@
           <t>Subset</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="n">
+        <v>2</v>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4059,14 +4063,14 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>hamming_accuracy_pa</t>
+          <t>abs</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>0.65729</v>
+        <v>0.07838000000000001</v>
       </c>
       <c r="I91" t="n">
-        <v>0.02962</v>
+        <v>0.04886</v>
       </c>
     </row>
     <row r="92">
@@ -4077,7 +4081,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__None</t>
+          <t>PreOrder__Subset__2</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4085,27 +4089,29 @@
           <t>Subset</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="n">
+        <v>2</v>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>PreferenceOrder</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>subset0_1_pa</t>
+          <t>hamming_accuracy_PRE_ORDER</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>0.23277</v>
+        <v>0.39261</v>
       </c>
       <c r="I92" t="n">
-        <v>0.0562</v>
+        <v>0.01544</v>
       </c>
     </row>
     <row r="93">
@@ -4116,7 +4122,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__None</t>
+          <t>PreOrder__Subset__2</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4124,27 +4130,29 @@
           <t>Subset</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="n">
+        <v>2</v>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>PartialOrder</t>
+          <t>PreOrder</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>PreferenceOrder</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>f1_pa</t>
+          <t>subset0_1_PRE_ORDER</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>0.58878</v>
+        <v>0.0027</v>
       </c>
       <c r="I93" t="n">
-        <v>0.04683</v>
+        <v>0.00413</v>
       </c>
     </row>
     <row r="94">
@@ -4155,12 +4163,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__None</t>
+          <t>PartialOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Subset</t>
+          <t>Hamming</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -4171,19 +4179,19 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>arec</t>
+          <t>hamming_accuracy</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>0.77207</v>
+        <v>0.58378</v>
       </c>
       <c r="I94" t="n">
-        <v>0.0324</v>
+        <v>0.02165</v>
       </c>
     </row>
     <row r="95">
@@ -4194,12 +4202,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__None</t>
+          <t>PartialOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Subset</t>
+          <t>Hamming</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -4210,19 +4218,19 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>aabs</t>
+          <t>subset0_1</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>0.33634</v>
+        <v>0.04955</v>
       </c>
       <c r="I95" t="n">
-        <v>0.06204</v>
+        <v>0.01943</v>
       </c>
     </row>
     <row r="96">
@@ -4233,12 +4241,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__None</t>
+          <t>PartialOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Subset</t>
+          <t>Hamming</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -4249,19 +4257,19 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>f1</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>0.27117</v>
+        <v>0.59832</v>
       </c>
       <c r="I96" t="n">
-        <v>0.07246</v>
+        <v>0.02656</v>
       </c>
     </row>
     <row r="97">
@@ -4272,12 +4280,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__None</t>
+          <t>PartialOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Subset</t>
+          <t>Hamming</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -4288,19 +4296,19 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>abs</t>
+          <t>jaccard</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>0.81532</v>
+        <v>0.46607</v>
       </c>
       <c r="I97" t="n">
-        <v>0.03279</v>
+        <v>0.02508</v>
       </c>
     </row>
     <row r="98">
@@ -4311,12 +4319,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__None</t>
+          <t>PartialOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Subset</t>
+          <t>Hamming</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -4327,19 +4335,19 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>PreferenceOrder</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>hamming_accuracy_PARTIAL_ORDER</t>
+          <t>macro_f1</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>0.48883</v>
+        <v>0.5243100000000001</v>
       </c>
       <c r="I98" t="n">
-        <v>0.0125</v>
+        <v>0.02626</v>
       </c>
     </row>
     <row r="99">
@@ -4350,12 +4358,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__None</t>
+          <t>PartialOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Subset</t>
+          <t>Hamming</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -4366,19 +4374,19 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>PreferenceOrder</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>subset0_1_PARTIAL_ORDER</t>
+          <t>micro_f1</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>0.0018</v>
+        <v>0.62205</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0036</v>
+        <v>0.02367</v>
       </c>
     </row>
     <row r="100">
@@ -4389,17 +4397,15 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__2</t>
+          <t>PartialOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>2</v>
-      </c>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>PartialOrder</t>
@@ -4412,14 +4418,14 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>hamming_accuracy</t>
+          <t>macro_precision</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>0.58213</v>
+        <v>0.44251</v>
       </c>
       <c r="I100" t="n">
-        <v>0.02297</v>
+        <v>0.02438</v>
       </c>
     </row>
     <row r="101">
@@ -4430,17 +4436,15 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__2</t>
+          <t>PartialOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>2</v>
-      </c>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>PartialOrder</t>
@@ -4453,14 +4457,14 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>subset0_1</t>
+          <t>micro_precision</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>0.04865</v>
+        <v>0.51031</v>
       </c>
       <c r="I101" t="n">
-        <v>0.01765</v>
+        <v>0.0234</v>
       </c>
     </row>
     <row r="102">
@@ -4471,17 +4475,15 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__2</t>
+          <t>PartialOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>2</v>
-      </c>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>PartialOrder</t>
@@ -4494,14 +4496,14 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>f1</t>
+          <t>macro_recall</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>0.59395</v>
+        <v>0.69825</v>
       </c>
       <c r="I102" t="n">
-        <v>0.02799</v>
+        <v>0.0678</v>
       </c>
     </row>
     <row r="103">
@@ -4512,17 +4514,15 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__2</t>
+          <t>PartialOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>2</v>
-      </c>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>PartialOrder</t>
@@ -4535,14 +4535,14 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>mfrd</t>
+          <t>micro_recall</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>0.84228</v>
+        <v>0.79798</v>
       </c>
       <c r="I103" t="n">
-        <v>0.04486</v>
+        <v>0.03875</v>
       </c>
     </row>
     <row r="104">
@@ -4553,17 +4553,15 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__2</t>
+          <t>PartialOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>2</v>
-      </c>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>PartialOrder</t>
@@ -4576,14 +4574,14 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>afrd</t>
+          <t>example_precision</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>0.48033</v>
+        <v>0.52234</v>
       </c>
       <c r="I104" t="n">
-        <v>0.06512</v>
+        <v>0.02763</v>
       </c>
     </row>
     <row r="105">
@@ -4594,17 +4592,15 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__2</t>
+          <t>PartialOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>2</v>
-      </c>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>PartialOrder</t>
@@ -4612,19 +4608,19 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>hamming_accuracy_pa</t>
+          <t>example_recall</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>0.65581</v>
+        <v>0.78492</v>
       </c>
       <c r="I105" t="n">
-        <v>0.03161</v>
+        <v>0.04265</v>
       </c>
     </row>
     <row r="106">
@@ -4635,17 +4631,15 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__2</t>
+          <t>PartialOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>2</v>
-      </c>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>PartialOrder</t>
@@ -4653,19 +4647,19 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>subset0_1_pa</t>
+          <t>mfrd</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>0.22631</v>
+        <v>0.85219</v>
       </c>
       <c r="I106" t="n">
-        <v>0.06001</v>
+        <v>0.05026</v>
       </c>
     </row>
     <row r="107">
@@ -4676,17 +4670,15 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__2</t>
+          <t>PartialOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>2</v>
-      </c>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>PartialOrder</t>
@@ -4694,19 +4686,19 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>PartialAbstention</t>
+          <t>BinaryVector</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>f1_pa</t>
+          <t>afrd</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>0.58224</v>
+        <v>0.49316</v>
       </c>
       <c r="I107" t="n">
-        <v>0.04738</v>
+        <v>0.06327000000000001</v>
       </c>
     </row>
     <row r="108">
@@ -4717,17 +4709,15 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__2</t>
+          <t>PartialOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>2</v>
-      </c>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>PartialOrder</t>
@@ -4740,14 +4730,14 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>arec</t>
+          <t>hamming_accuracy_pa</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>0.77147</v>
+        <v>0.65752</v>
       </c>
       <c r="I108" t="n">
-        <v>0.03327</v>
+        <v>0.02966</v>
       </c>
     </row>
     <row r="109">
@@ -4758,17 +4748,15 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__2</t>
+          <t>PartialOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>2</v>
-      </c>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>PartialOrder</t>
@@ -4781,14 +4769,14 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>aabs</t>
+          <t>subset0_1_pa</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>0.33754</v>
+        <v>0.23186</v>
       </c>
       <c r="I109" t="n">
-        <v>0.06173</v>
+        <v>0.05621</v>
       </c>
     </row>
     <row r="110">
@@ -4799,17 +4787,15 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__2</t>
+          <t>PartialOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>2</v>
-      </c>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>PartialOrder</t>
@@ -4822,14 +4808,14 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>f1_pa</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>0.26486</v>
+        <v>0.5889799999999999</v>
       </c>
       <c r="I110" t="n">
-        <v>0.07678</v>
+        <v>0.04674</v>
       </c>
     </row>
     <row r="111">
@@ -4840,17 +4826,15 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__2</t>
+          <t>PartialOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>2</v>
-      </c>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>PartialOrder</t>
@@ -4863,14 +4847,14 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>abs</t>
+          <t>arec</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>0.8162199999999999</v>
+        <v>0.77222</v>
       </c>
       <c r="I111" t="n">
-        <v>0.03228</v>
+        <v>0.03242</v>
       </c>
     </row>
     <row r="112">
@@ -4881,17 +4865,15 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PartialOrder__Subset__2</t>
+          <t>PartialOrder__Hamming__None</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>2</v>
-      </c>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>PartialOrder</t>
@@ -4899,19 +4881,19 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>PreferenceOrder</t>
+          <t>PartialAbstention</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>hamming_accuracy_PARTIAL_ORDER</t>
+          <t>aabs</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>0.48805</v>
+        <v>0.33634</v>
       </c>
       <c r="I112" t="n">
-        <v>0.01237</v>
+        <v>0.06214</v>
       </c>
     </row>
     <row r="113">
@@ -4922,36 +4904,2934 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
+          <t>PartialOrder__Hamming__None</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>PartialAbstention</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>rec</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>0.27027</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0.07285999999999999</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>PartialOrder__Hamming__None</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>PartialAbstention</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>abs</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>0.81351</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0.03372</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>PartialOrder__Hamming__None</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>PreferenceOrder</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>hamming_accuracy_PARTIAL_ORDER</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>0.48865</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.01236</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>PartialOrder__Hamming__None</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>PreferenceOrder</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>subset0_1_PARTIAL_ORDER</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0.0036</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>PartialOrder__Hamming__2</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>2</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>hamming_accuracy</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>0.58318</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.02324</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>PartialOrder__Hamming__2</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>2</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>subset0_1</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>0.05045</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.0214</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>PartialOrder__Hamming__2</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>2</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>0.59492</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.02851</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>PartialOrder__Hamming__2</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>2</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>jaccard</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>0.46306</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.02804</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>PartialOrder__Hamming__2</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>2</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>macro_f1</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>0.52094</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.028</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>PartialOrder__Hamming__2</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>2</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>micro_f1</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>0.61895</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.02571</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>PartialOrder__Hamming__2</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>2</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>macro_precision</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>0.44152</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.02669</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>PartialOrder__Hamming__2</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>2</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>micro_precision</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>0.51002</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.02549</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>PartialOrder__Hamming__2</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>2</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>macro_recall</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>0.6893899999999999</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.06954</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>PartialOrder__Hamming__2</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>2</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>micro_recall</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>0.78883</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.04139</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>PartialOrder__Hamming__2</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>2</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>example_precision</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>0.52294</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.03002</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>PartialOrder__Hamming__2</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>2</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>example_recall</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>0.77539</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.04512</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>PartialOrder__Hamming__2</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>2</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>mfrd</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>0.84227</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.04654</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>PartialOrder__Hamming__2</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>2</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>afrd</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>0.4822</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.06396</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>PartialOrder__Hamming__2</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>2</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>PartialAbstention</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>hamming_accuracy_pa</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>0.65642</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.03232</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>PartialOrder__Hamming__2</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>2</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>PartialAbstention</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>subset0_1_pa</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>0.22635</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.06183</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>PartialOrder__Hamming__2</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>2</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>PartialAbstention</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>f1_pa</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>0.58301</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.04886</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>PartialOrder__Hamming__2</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>2</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>PartialAbstention</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>arec</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>0.77177</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.03368</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>PartialOrder__Hamming__2</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>2</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>PartialAbstention</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>aabs</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.06216</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>PartialOrder__Hamming__2</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>2</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>PartialAbstention</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>rec</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>0.26486</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.07846</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>PartialOrder__Hamming__2</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>2</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>PartialAbstention</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>abs</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>0.81351</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.03324</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>PartialOrder__Hamming__2</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>2</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>PreferenceOrder</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>hamming_accuracy_PARTIAL_ORDER</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>0.48799</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.01275</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>PartialOrder__Hamming__2</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Hamming</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>2</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>PreferenceOrder</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>subset0_1_PARTIAL_ORDER</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.0036</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__None</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>hamming_accuracy</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>0.58333</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.02135</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__None</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>subset0_1</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>0.04955</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.01943</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__None</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>0.59798</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.02595</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__None</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>jaccard</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>0.46578</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.02473</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__None</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>macro_f1</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>0.5243100000000001</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0.02619</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__None</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>micro_f1</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>0.62191</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0.02328</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__None</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>macro_precision</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>0.44235</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0.02455</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__None</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>micro_precision</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>0.50998</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0.02335</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__None</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>macro_recall</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>0.69836</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0.06736</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__None</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>micro_recall</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>0.79832</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0.03765</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__None</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>example_precision</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>0.5213100000000001</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0.02733</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__None</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>example_recall</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>0.78508</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0.04161</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__None</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>mfrd</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>0.85336</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0.04952</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__None</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>afrd</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>0.49298</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0.06448</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__None</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>PartialAbstention</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>hamming_accuracy_pa</t>
+        </is>
+      </c>
+      <c r="H154" t="n">
+        <v>0.65729</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0.02962</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__None</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>PartialAbstention</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>subset0_1_pa</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>0.23277</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0.0562</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__None</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>PartialAbstention</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>f1_pa</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>0.58878</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0.04683</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__None</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>PartialAbstention</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>arec</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>0.77207</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0.0324</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__None</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>PartialAbstention</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>aabs</t>
+        </is>
+      </c>
+      <c r="H158" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0.06204</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__None</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>PartialAbstention</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>rec</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>0.27117</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0.07246</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__None</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>PartialAbstention</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>abs</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>0.81532</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0.03279</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__None</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>PreferenceOrder</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>hamming_accuracy_PARTIAL_ORDER</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
+        <v>0.48883</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0.0125</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__None</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>PreferenceOrder</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>subset0_1_PARTIAL_ORDER</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0.0036</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
           <t>PartialOrder__Subset__2</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Subset</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>2</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>PartialOrder</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>2</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>hamming_accuracy</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
+        <v>0.58213</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0.02297</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__2</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>2</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>subset0_1</t>
+        </is>
+      </c>
+      <c r="H164" t="n">
+        <v>0.04865</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0.01765</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__2</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>2</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="H165" t="n">
+        <v>0.59395</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0.02799</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__2</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>2</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>jaccard</t>
+        </is>
+      </c>
+      <c r="H166" t="n">
+        <v>0.46186</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0.0274</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__2</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>2</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>macro_f1</t>
+        </is>
+      </c>
+      <c r="H167" t="n">
+        <v>0.5200900000000001</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0.02788</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__2</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>2</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>micro_f1</t>
+        </is>
+      </c>
+      <c r="H168" t="n">
+        <v>0.6180600000000001</v>
+      </c>
+      <c r="I168" t="n">
+        <v>0.02542</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__2</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>2</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>macro_precision</t>
+        </is>
+      </c>
+      <c r="H169" t="n">
+        <v>0.4409</v>
+      </c>
+      <c r="I169" t="n">
+        <v>0.02626</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__2</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>2</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>micro_precision</t>
+        </is>
+      </c>
+      <c r="H170" t="n">
+        <v>0.50918</v>
+      </c>
+      <c r="I170" t="n">
+        <v>0.02472</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__2</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>2</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>macro_recall</t>
+        </is>
+      </c>
+      <c r="H171" t="n">
+        <v>0.68829</v>
+      </c>
+      <c r="I171" t="n">
+        <v>0.06923</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__2</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>2</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>micro_recall</t>
+        </is>
+      </c>
+      <c r="H172" t="n">
+        <v>0.78781</v>
+      </c>
+      <c r="I172" t="n">
+        <v>0.04116</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__2</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>2</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>example_precision</t>
+        </is>
+      </c>
+      <c r="H173" t="n">
+        <v>0.52138</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0.02867</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__2</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>2</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>example_recall</t>
+        </is>
+      </c>
+      <c r="H174" t="n">
+        <v>0.77471</v>
+      </c>
+      <c r="I174" t="n">
+        <v>0.04464</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__2</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>2</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>mfrd</t>
+        </is>
+      </c>
+      <c r="H175" t="n">
+        <v>0.84228</v>
+      </c>
+      <c r="I175" t="n">
+        <v>0.04486</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__2</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>2</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>BinaryVector</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>afrd</t>
+        </is>
+      </c>
+      <c r="H176" t="n">
+        <v>0.48033</v>
+      </c>
+      <c r="I176" t="n">
+        <v>0.06512</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__2</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>2</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>PartialAbstention</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>hamming_accuracy_pa</t>
+        </is>
+      </c>
+      <c r="H177" t="n">
+        <v>0.65581</v>
+      </c>
+      <c r="I177" t="n">
+        <v>0.03161</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__2</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>2</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>PartialAbstention</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>subset0_1_pa</t>
+        </is>
+      </c>
+      <c r="H178" t="n">
+        <v>0.22631</v>
+      </c>
+      <c r="I178" t="n">
+        <v>0.06001</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__2</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>2</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>PartialAbstention</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>f1_pa</t>
+        </is>
+      </c>
+      <c r="H179" t="n">
+        <v>0.58224</v>
+      </c>
+      <c r="I179" t="n">
+        <v>0.04738</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__2</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>2</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>PartialAbstention</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>arec</t>
+        </is>
+      </c>
+      <c r="H180" t="n">
+        <v>0.77147</v>
+      </c>
+      <c r="I180" t="n">
+        <v>0.03327</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__2</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>2</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>PartialAbstention</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>aabs</t>
+        </is>
+      </c>
+      <c r="H181" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="I181" t="n">
+        <v>0.06173</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__2</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>2</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>PartialAbstention</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>rec</t>
+        </is>
+      </c>
+      <c r="H182" t="n">
+        <v>0.26486</v>
+      </c>
+      <c r="I182" t="n">
+        <v>0.07678</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__2</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>2</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>PartialAbstention</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>abs</t>
+        </is>
+      </c>
+      <c r="H183" t="n">
+        <v>0.8162199999999999</v>
+      </c>
+      <c r="I183" t="n">
+        <v>0.03228</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__2</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>2</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
         <is>
           <t>PreferenceOrder</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>hamming_accuracy_PARTIAL_ORDER</t>
+        </is>
+      </c>
+      <c r="H184" t="n">
+        <v>0.48805</v>
+      </c>
+      <c r="I184" t="n">
+        <v>0.01237</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>PartialOrder__Subset__2</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>2</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>PartialOrder</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>PreferenceOrder</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
         <is>
           <t>subset0_1_PARTIAL_ORDER</t>
         </is>
       </c>
-      <c r="H113" t="n">
+      <c r="H185" t="n">
         <v>0.0018</v>
       </c>
-      <c r="I113" t="n">
+      <c r="I185" t="n">
         <v>0.0036</v>
       </c>
     </row>
